--- a/rules/CORE-000305/positive/01/data/unit-test-coreid-FB4005-positive.xlsx
+++ b/rules/CORE-000305/positive/01/data/unit-test-coreid-FB4005-positive.xlsx
@@ -1249,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1732,6 +1732,81 @@
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>2013-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ASPIRIN</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>PRN</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2012-08</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>P2 days</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>2013-05-20</t>
         </is>
